--- a/output/roomself_excel/6565.xlsx
+++ b/output/roomself_excel/6565.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>312614</v>
+        <v>94868</v>
       </c>
       <c r="D2" t="n">
-        <v>7152</v>
+        <v>2564</v>
       </c>
       <c r="E2" t="n">
-        <v>1045</v>
+        <v>242</v>
       </c>
       <c r="F2" t="n">
-        <v>283</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7372</v>
+        <v>189192</v>
       </c>
       <c r="D3" t="n">
-        <v>692</v>
+        <v>3492</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>490</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>109875</v>
+        <v>101798</v>
       </c>
       <c r="D4" t="n">
-        <v>2672</v>
+        <v>2648</v>
       </c>
       <c r="E4" t="n">
-        <v>293</v>
+        <v>252</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>226389</v>
+        <v>109875</v>
       </c>
       <c r="D5" t="n">
-        <v>3880</v>
+        <v>2672</v>
       </c>
       <c r="E5" t="n">
-        <v>598</v>
+        <v>293</v>
       </c>
       <c r="F5" t="n">
-        <v>410</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>706380</v>
+        <v>118420</v>
       </c>
       <c r="D7" t="n">
-        <v>14480</v>
+        <v>2780</v>
       </c>
       <c r="E7" t="n">
-        <v>1050</v>
+        <v>481</v>
       </c>
       <c r="F7" t="n">
-        <v>996</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17136</v>
+        <v>106970</v>
       </c>
       <c r="D8" t="n">
-        <v>1048</v>
+        <v>2812</v>
       </c>
       <c r="E8" t="n">
-        <v>126</v>
+        <v>419</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11832</v>
+        <v>17136</v>
       </c>
       <c r="D9" t="n">
-        <v>892</v>
+        <v>1048</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="F9" t="n">
         <v>20</v>
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31450</v>
+        <v>11832</v>
       </c>
       <c r="D10" t="n">
-        <v>1420</v>
+        <v>892</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>153304</v>
+        <v>31450</v>
       </c>
       <c r="D11" t="n">
-        <v>3716</v>
+        <v>1420</v>
       </c>
       <c r="E11" t="n">
-        <v>533</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>106970</v>
+        <v>153304</v>
       </c>
       <c r="D12" t="n">
-        <v>2812</v>
+        <v>3716</v>
       </c>
       <c r="E12" t="n">
-        <v>419</v>
+        <v>533</v>
       </c>
       <c r="F12" t="n">
-        <v>324</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>53766</v>
+        <v>112706</v>
       </c>
       <c r="D13" t="n">
-        <v>1868</v>
+        <v>2912</v>
       </c>
       <c r="E13" t="n">
-        <v>280</v>
+        <v>483</v>
       </c>
       <c r="F13" t="n">
-        <v>225</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
@@ -730,17 +730,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>36890</v>
+        <v>7372</v>
       </c>
       <c r="D14" t="n">
-        <v>1548</v>
+        <v>692</v>
       </c>
       <c r="E14" t="n">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
         <v>19</v>
@@ -756,16 +756,126 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>202102</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7048</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>18720</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>1104</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>156</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>226389</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3880</v>
+      </c>
+      <c r="E17" t="n">
+        <v>598</v>
+      </c>
+      <c r="F17" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>199908</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5296</v>
+      </c>
+      <c r="E18" t="n">
+        <v>562</v>
+      </c>
+      <c r="F18" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>53766</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1868</v>
+      </c>
+      <c r="E19" t="n">
+        <v>280</v>
+      </c>
+      <c r="F19" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>36890</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1548</v>
+      </c>
+      <c r="E20" t="n">
+        <v>170</v>
+      </c>
+      <c r="F20" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/6565.xlsx
+++ b/output/roomself_excel/6565.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2564</v>
       </c>
-      <c r="E2" t="n">
-        <v>242</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>126</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>3492</v>
       </c>
-      <c r="E3" t="n">
-        <v>490</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>412</v>
+        <v>402</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>470</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>2648</v>
       </c>
-      <c r="E4" t="n">
-        <v>252</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>126</v>
+        <v>399</v>
+      </c>
+      <c r="G4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>251</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +601,20 @@
       <c r="D5" t="n">
         <v>2672</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>293</v>
       </c>
-      <c r="F5" t="n">
-        <v>19</v>
-      </c>
+      <c r="G5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +631,27 @@
       <c r="D6" t="n">
         <v>2448</v>
       </c>
-      <c r="E6" t="n">
-        <v>385</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>267</v>
+        <v>247</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>365</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +669,20 @@
       <c r="D7" t="n">
         <v>2780</v>
       </c>
-      <c r="E7" t="n">
-        <v>481</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>315</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +699,27 @@
       <c r="D8" t="n">
         <v>2812</v>
       </c>
-      <c r="E8" t="n">
-        <v>419</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>324</v>
+        <v>399</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>304</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +737,20 @@
       <c r="D9" t="n">
         <v>1048</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>126</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>20</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +767,20 @@
       <c r="D10" t="n">
         <v>892</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>87</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>20</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +797,12 @@
       <c r="D11" t="n">
         <v>1420</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +819,27 @@
       <c r="D12" t="n">
         <v>3716</v>
       </c>
-      <c r="E12" t="n">
-        <v>533</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>434</v>
+        <v>141</v>
+      </c>
+      <c r="G12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>295</v>
+      </c>
+      <c r="J12" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -717,11 +857,27 @@
       <c r="D13" t="n">
         <v>2912</v>
       </c>
-      <c r="E13" t="n">
-        <v>483</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>207</v>
+        <v>175</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>464</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -739,12 +895,20 @@
       <c r="D14" t="n">
         <v>692</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>76</v>
       </c>
-      <c r="F14" t="n">
-        <v>19</v>
-      </c>
+      <c r="G14" t="n">
+        <v>19</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +925,20 @@
       <c r="D15" t="n">
         <v>7048</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="G15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +955,20 @@
       <c r="D16" t="n">
         <v>1104</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>156</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>20</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,11 +985,27 @@
       <c r="D17" t="n">
         <v>3880</v>
       </c>
-      <c r="E17" t="n">
-        <v>598</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>410</v>
+        <v>391</v>
+      </c>
+      <c r="G17" t="n">
+        <v>19</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>579</v>
+      </c>
+      <c r="J17" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -827,11 +1023,27 @@
       <c r="D18" t="n">
         <v>5296</v>
       </c>
-      <c r="E18" t="n">
-        <v>562</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>283</v>
+        <v>543</v>
+      </c>
+      <c r="G18" t="n">
+        <v>19</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>264</v>
+      </c>
+      <c r="J18" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -849,11 +1061,27 @@
       <c r="D19" t="n">
         <v>1868</v>
       </c>
-      <c r="E19" t="n">
-        <v>280</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>225</v>
+        <v>261</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>206</v>
+      </c>
+      <c r="J19" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -871,12 +1099,20 @@
       <c r="D20" t="n">
         <v>1548</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>170</v>
       </c>
-      <c r="F20" t="n">
-        <v>19</v>
-      </c>
+      <c r="G20" t="n">
+        <v>19</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
